--- a/static/Files/Template - GPCRome wheel - Text.xlsx
+++ b/static/Files/Template - GPCRome wheel - Text.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcs839\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA153A-355A-44BE-AB48-68D9ED616347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131D1CCA-5CE7-4D9D-A405-BDCAA8AFE247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GPCRome wheel - Text" sheetId="6" r:id="rId1"/>
     <sheet name="GPCR lookup table" sheetId="7" r:id="rId2"/>
+    <sheet name="Example - Dataset 1" sheetId="8" r:id="rId3"/>
+    <sheet name="Example - Dataset 2" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPCR lookup table'!$A$1:$D$805</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GPCRome wheel - Text'!#REF!</definedName>
+    <definedName name="GPCRome_list" localSheetId="3">_xlfn._xlws.FILTER(ReceptorData[GPCRs
+(UniProt)],#REF!= "Yes")</definedName>
     <definedName name="GPCRome_list">_xlfn._xlws.FILTER(ReceptorData[GPCRs
 (UniProt)],#REF!= "Yes")</definedName>
   </definedNames>
@@ -43,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="739">
   <si>
     <t>Class</t>
   </si>
@@ -324,9 +328,6 @@
     <t>Amino acid receptors</t>
   </si>
   <si>
-    <t>GABA&lt;sub&gt;B&lt;/sub&gt; receptors</t>
-  </si>
-  <si>
     <t>Metabotropic glutamate receptors</t>
   </si>
   <si>
@@ -355,9 +356,6 @@
   </si>
   <si>
     <t>Other GPCR orphans</t>
-  </si>
-  <si>
-    <t>Other GPCRs</t>
   </si>
   <si>
     <t>Info / error</t>
@@ -2254,12 +2252,85 @@
       <t>(Gene or Uniprot name)</t>
     </r>
   </si>
+  <si>
+    <t>Label 1</t>
+  </si>
+  <si>
+    <t>Label 3</t>
+  </si>
+  <si>
+    <t>Label 2</t>
+  </si>
+  <si>
+    <t>Label 4</t>
+  </si>
+  <si>
+    <t>Label 5</t>
+  </si>
+  <si>
+    <t>Label 6</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GPCRs
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Gene or Uniprot name)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Add words
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Visualized as different colors)</t>
+    </r>
+  </si>
+  <si>
+    <t>#CC00CC</t>
+  </si>
+  <si>
+    <t>OPSX</t>
+  </si>
+  <si>
+    <t>RRH</t>
+  </si>
+  <si>
+    <t>GABAB receptors</t>
+  </si>
+  <si>
+    <t>Classless</t>
+  </si>
+  <si>
+    <t>#66FF33</t>
+  </si>
+  <si>
+    <t>#9B9B9B</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2323,8 +2394,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2343,8 +2450,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD05F12"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD85D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2417,11 +2566,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2470,15 +2634,157 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2512,124 +2818,6 @@
           <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2836,6 +3024,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC00CC"/>
+      <color rgb="FFFFD85D"/>
+      <color rgb="FFD05F12"/>
       <color rgb="FF87B6E1"/>
       <color rgb="FF00D661"/>
       <color rgb="FF25A2FF"/>
@@ -2884,17 +3075,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F6FC1CD-B142-4F94-8C86-4E8AE110AD29}" name="ReceptorData" displayName="ReceptorData" ref="A1:E398" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:E398" xr:uid="{8F6FC1CD-B142-4F94-8C86-4E8AE110AD29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F6FC1CD-B142-4F94-8C86-4E8AE110AD29}" name="ReceptorData" displayName="ReceptorData" ref="A1:E399" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0">
+  <autoFilter ref="A1:E399" xr:uid="{8F6FC1CD-B142-4F94-8C86-4E8AE110AD29}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D398">
     <sortCondition ref="D1:D398"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7EFCA3FF-1755-4B34-A3E6-68FEC263B14E}" name="GPCRs_x000a_(UniProt)" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{BEF0682F-C1C7-43DC-B2F7-E432261E366A}" name="GPCRs_x000a_(Gene name)" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D2ED2812-3409-4307-924A-E866BD70C70B}" name="Receptor family" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{33ED79F7-22B3-4243-BABD-052ACEAEF199}" name="Ligand type" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{F1018DDD-C294-4ACD-8BAC-62B3126D9844}" name="Class" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{7EFCA3FF-1755-4B34-A3E6-68FEC263B14E}" name="GPCRs_x000a_(UniProt)" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{BEF0682F-C1C7-43DC-B2F7-E432261E366A}" name="GPCRs_x000a_(Gene name)" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D2ED2812-3409-4307-924A-E866BD70C70B}" name="Receptor family" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{33ED79F7-22B3-4243-BABD-052ACEAEF199}" name="Ligand type" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{F1018DDD-C294-4ACD-8BAC-62B3126D9844}" name="Class" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3163,7 +3354,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E552C984-CB4E-45B6-83C9-925F4E5D96AD}">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1">
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
   <dimension ref="A1:E398"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3176,26 +3369,26 @@
   <sheetData>
     <row r="1" spans="1:5" ht="70" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>108</v>
-      </c>
       <c r="D1" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="9" t="str">
         <f>IF(A2="",
     IF(B2&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3214,10 +3407,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="12"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="8" t="str">
         <f>IF(A3="",
     IF(B3&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3236,10 +3429,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="8" t="str">
         <f>IF(A4="",
     IF(B4&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3258,10 +3451,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="12"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="8" t="str">
         <f>IF(A5="",
     IF(B5&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3280,10 +3473,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="12"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="8" t="str">
         <f>IF(A6="",
     IF(B6&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3302,10 +3495,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="12"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="8" t="str">
         <f>IF(A7="",
     IF(B7&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3324,10 +3517,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="12"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="8" t="str">
         <f>IF(A8="",
     IF(B8&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3346,10 +3539,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="8" t="str">
         <f>IF(A9="",
     IF(B9&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3368,10 +3561,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="8" t="str">
         <f>IF(A10="",
     IF(B10&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3390,10 +3583,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="8" t="str">
         <f>IF(A11="",
     IF(B11&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3412,10 +3605,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="8" t="str">
         <f>IF(A12="",
     IF(B12&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3434,10 +3627,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="8" t="str">
         <f>IF(A13="",
     IF(B13&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3456,10 +3649,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="8" t="str">
         <f>IF(A14="",
     IF(B14&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3478,10 +3671,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="12"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="8" t="str">
         <f>IF(A15="",
     IF(B15&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3500,10 +3693,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="12"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="8" t="str">
         <f>IF(A16="",
     IF(B16&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3522,10 +3715,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="8" t="str">
         <f>IF(A17="",
     IF(B17&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3544,10 +3737,10 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="12"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="20"/>
       <c r="E18" s="8" t="str">
         <f>IF(A18="",
     IF(B18&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3566,10 +3759,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="8" t="str">
         <f>IF(A19="",
     IF(B19&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3588,10 +3781,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="20"/>
       <c r="E20" s="8" t="str">
         <f>IF(A20="",
     IF(B20&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3610,10 +3803,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="8" t="str">
         <f>IF(A21="",
     IF(B21&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3632,10 +3825,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="12"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="20"/>
       <c r="E22" s="8" t="str">
         <f>IF(A22="",
     IF(B22&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3654,10 +3847,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="12"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="23"/>
       <c r="E23" s="6" t="str">
         <f>IF(A23="",
     IF(B23&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3676,10 +3869,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="20"/>
       <c r="E24" s="6" t="str">
         <f>IF(A24="",
     IF(B24&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3698,10 +3891,10 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="12"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="6" t="str">
         <f>IF(A25="",
     IF(B25&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3720,10 +3913,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="12"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="20"/>
       <c r="E26" s="6" t="str">
         <f>IF(A26="",
     IF(B26&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3742,10 +3935,10 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="12"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="6" t="str">
         <f>IF(A27="",
     IF(B27&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3764,10 +3957,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="12"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="6" t="str">
         <f>IF(A28="",
     IF(B28&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3786,10 +3979,10 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="6" t="str">
         <f>IF(A29="",
     IF(B29&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3808,10 +4001,10 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="20"/>
       <c r="E30" s="6" t="str">
         <f>IF(A30="",
     IF(B30&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3830,10 +4023,10 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="6" t="str">
         <f>IF(A31="",
     IF(B31&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3852,10 +4045,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="20"/>
       <c r="E32" s="6" t="str">
         <f>IF(A32="",
     IF(B32&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3874,10 +4067,10 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="3"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="6" t="str">
         <f>IF(A33="",
     IF(B33&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3896,10 +4089,10 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="20"/>
       <c r="E34" s="6" t="str">
         <f>IF(A34="",
     IF(B34&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3918,10 +4111,10 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="6" t="str">
         <f>IF(A35="",
     IF(B35&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3940,10 +4133,10 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="20"/>
       <c r="E36" s="6" t="str">
         <f>IF(A36="",
     IF(B36&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -3962,10 +4155,10 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="6" t="str">
         <f>IF(A37="",
     IF(B37&lt;&gt;"", "You need to select a GPCR.", ""),
@@ -11928,16 +12121,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E398">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>E2="Invalid GPCR (Try to take a look at the 'GPCR lookup table' Sheet)."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>E2="You need to select a GPCR."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>E2="You need to add text in column B."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>E2="Correctly formatted."</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11951,12 +12144,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E4F9080-6D73-42FD-974C-7FB5526D6787}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E398"/>
+  <sheetPr codeName="Sheet2">
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="17.6328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
@@ -11964,16 +12158,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>0</v>
@@ -11981,10 +12175,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>3</v>
@@ -11992,16 +12186,16 @@
       <c r="D2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
@@ -12015,10 +12209,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>3</v>
@@ -12032,10 +12226,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
@@ -12049,10 +12243,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
@@ -12066,10 +12260,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
@@ -12083,10 +12277,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>3</v>
@@ -12100,10 +12294,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
@@ -12117,10 +12311,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
@@ -12134,10 +12328,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
@@ -12151,10 +12345,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
@@ -12168,10 +12362,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
@@ -12185,10 +12379,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>44</v>
@@ -12202,10 +12396,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>44</v>
@@ -12219,10 +12413,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>44</v>
@@ -12236,10 +12430,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>44</v>
@@ -12253,10 +12447,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>4</v>
@@ -12270,10 +12464,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>4</v>
@@ -12287,10 +12481,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>4</v>
@@ -12304,10 +12498,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>4</v>
@@ -12321,10 +12515,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>4</v>
@@ -12338,10 +12532,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>23</v>
@@ -12355,10 +12549,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>5</v>
@@ -12372,10 +12566,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -12389,10 +12583,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>5</v>
@@ -12406,10 +12600,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>5</v>
@@ -12423,10 +12617,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>5</v>
@@ -12440,10 +12634,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>5</v>
@@ -12457,10 +12651,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>5</v>
@@ -12474,10 +12668,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>5</v>
@@ -12491,10 +12685,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>5</v>
@@ -12508,10 +12702,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>10</v>
@@ -12525,10 +12719,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>10</v>
@@ -12542,10 +12736,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>11</v>
@@ -12559,10 +12753,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>13</v>
@@ -12576,10 +12770,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>13</v>
@@ -12593,10 +12787,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>12</v>
@@ -12610,10 +12804,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>15</v>
@@ -12627,10 +12821,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>15</v>
@@ -12644,10 +12838,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>15</v>
@@ -12661,10 +12855,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>14</v>
@@ -12678,10 +12872,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>44</v>
@@ -12695,10 +12889,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>44</v>
@@ -12712,10 +12906,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>44</v>
@@ -12729,10 +12923,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>44</v>
@@ -12746,10 +12940,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>44</v>
@@ -12763,10 +12957,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>44</v>
@@ -12780,10 +12974,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>44</v>
@@ -12797,10 +12991,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>44</v>
@@ -12814,10 +13008,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>44</v>
@@ -12831,10 +13025,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>44</v>
@@ -12848,10 +13042,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>44</v>
@@ -12865,10 +13059,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>49</v>
@@ -12882,10 +13076,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>49</v>
@@ -12899,10 +13093,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>43</v>
@@ -12916,10 +13110,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>43</v>
@@ -12933,10 +13127,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>52</v>
@@ -12950,10 +13144,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>52</v>
@@ -12967,10 +13161,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>44</v>
@@ -12984,10 +13178,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>44</v>
@@ -13001,10 +13195,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>44</v>
@@ -13018,10 +13212,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>44</v>
@@ -13035,10 +13229,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>44</v>
@@ -13052,10 +13246,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>44</v>
@@ -13069,10 +13263,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>44</v>
@@ -13086,10 +13280,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>6</v>
@@ -13103,10 +13297,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>6</v>
@@ -13120,10 +13314,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>6</v>
@@ -13137,10 +13331,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>6</v>
@@ -13154,10 +13348,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>6</v>
@@ -13171,10 +13365,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>16</v>
@@ -13188,10 +13382,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>16</v>
@@ -13205,10 +13399,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>48</v>
@@ -13222,10 +13416,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>48</v>
@@ -13239,10 +13433,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>48</v>
@@ -13256,10 +13450,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>48</v>
@@ -13273,10 +13467,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>17</v>
@@ -13290,10 +13484,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>17</v>
@@ -13307,10 +13501,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>17</v>
@@ -13324,10 +13518,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>45</v>
@@ -13341,10 +13535,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>71</v>
@@ -13358,10 +13552,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>18</v>
@@ -13375,10 +13569,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>18</v>
@@ -13392,10 +13586,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>18</v>
@@ -13409,10 +13603,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>14</v>
@@ -13426,10 +13620,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>19</v>
@@ -13443,10 +13637,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>20</v>
@@ -13460,10 +13654,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>71</v>
@@ -13477,10 +13671,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>53</v>
@@ -13494,10 +13688,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>71</v>
@@ -13511,10 +13705,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>71</v>
@@ -13528,10 +13722,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>71</v>
@@ -13545,10 +13739,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>71</v>
@@ -13562,10 +13756,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>71</v>
@@ -13579,10 +13773,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>71</v>
@@ -13596,10 +13790,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>71</v>
@@ -13613,10 +13807,10 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>71</v>
@@ -13630,10 +13824,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>71</v>
@@ -13647,10 +13841,10 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>71</v>
@@ -13664,10 +13858,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>71</v>
@@ -13681,10 +13875,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>71</v>
@@ -13698,10 +13892,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>71</v>
@@ -13715,10 +13909,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>71</v>
@@ -13732,10 +13926,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>71</v>
@@ -13749,10 +13943,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>71</v>
@@ -13766,10 +13960,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>71</v>
@@ -13783,10 +13977,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>71</v>
@@ -13800,10 +13994,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>71</v>
@@ -13817,10 +14011,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>71</v>
@@ -13834,10 +14028,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>71</v>
@@ -13851,10 +14045,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>62</v>
@@ -13868,10 +14062,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>63</v>
@@ -13885,10 +14079,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>71</v>
@@ -13902,10 +14096,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>71</v>
@@ -13919,10 +14113,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>71</v>
@@ -13936,10 +14130,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>53</v>
@@ -13953,10 +14147,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>71</v>
@@ -13970,10 +14164,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>71</v>
@@ -13987,10 +14181,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C120" s="12" t="s">
         <v>71</v>
@@ -14004,10 +14198,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>71</v>
@@ -14021,10 +14215,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>71</v>
@@ -14038,10 +14232,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>71</v>
@@ -14055,10 +14249,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>71</v>
@@ -14072,10 +14266,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>71</v>
@@ -14089,10 +14283,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>71</v>
@@ -14106,10 +14300,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>71</v>
@@ -14123,10 +14317,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>71</v>
@@ -14140,10 +14334,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>71</v>
@@ -14157,10 +14351,10 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>71</v>
@@ -14174,10 +14368,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>71</v>
@@ -14191,10 +14385,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>71</v>
@@ -14208,10 +14402,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>71</v>
@@ -14225,10 +14419,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>48</v>
@@ -14242,10 +14436,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>71</v>
@@ -14259,10 +14453,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>71</v>
@@ -14276,10 +14470,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>53</v>
@@ -14293,10 +14487,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>71</v>
@@ -14310,10 +14504,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>71</v>
@@ -14327,10 +14521,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>71</v>
@@ -14344,10 +14538,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>71</v>
@@ -14361,10 +14555,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>71</v>
@@ -14378,10 +14572,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>71</v>
@@ -14395,10 +14589,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>71</v>
@@ -14412,10 +14606,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>71</v>
@@ -14429,10 +14623,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>71</v>
@@ -14446,10 +14640,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>71</v>
@@ -14463,10 +14657,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>71</v>
@@ -14480,10 +14674,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>71</v>
@@ -14497,10 +14691,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>12</v>
@@ -14514,10 +14708,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C151" s="12" t="s">
         <v>65</v>
@@ -14531,10 +14725,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>65</v>
@@ -14548,10 +14742,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>65</v>
@@ -14565,10 +14759,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>7</v>
@@ -14582,10 +14776,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>7</v>
@@ -14599,10 +14793,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>7</v>
@@ -14616,10 +14810,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>7</v>
@@ -14633,10 +14827,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>21</v>
@@ -14650,10 +14844,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>71</v>
@@ -14667,10 +14861,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>71</v>
@@ -14684,10 +14878,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>71</v>
@@ -14701,10 +14895,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C162" s="12" t="s">
         <v>50</v>
@@ -14718,10 +14912,10 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>50</v>
@@ -14735,10 +14929,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>50</v>
@@ -14752,10 +14946,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>50</v>
@@ -14769,10 +14963,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>50</v>
@@ -14786,10 +14980,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>50</v>
@@ -14803,10 +14997,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>45</v>
@@ -14820,10 +15014,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C169" s="12" t="s">
         <v>49</v>
@@ -14837,10 +15031,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>49</v>
@@ -14854,10 +15048,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>71</v>
@@ -14871,10 +15065,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C172" s="12" t="s">
         <v>71</v>
@@ -14888,10 +15082,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>23</v>
@@ -14905,10 +15099,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>23</v>
@@ -14922,10 +15116,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C175" s="12" t="s">
         <v>23</v>
@@ -14939,10 +15133,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C176" s="12" t="s">
         <v>22</v>
@@ -14956,10 +15150,10 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>22</v>
@@ -14973,10 +15167,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>71</v>
@@ -14990,10 +15184,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>71</v>
@@ -15007,10 +15201,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>71</v>
@@ -15024,10 +15218,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>71</v>
@@ -15041,10 +15235,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="12" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C182" s="12" t="s">
         <v>71</v>
@@ -15058,10 +15252,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>71</v>
@@ -15075,10 +15269,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>71</v>
@@ -15092,10 +15286,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C185" s="12" t="s">
         <v>71</v>
@@ -15109,10 +15303,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>23</v>
@@ -15126,10 +15320,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>24</v>
@@ -15143,10 +15337,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>57</v>
@@ -15160,10 +15354,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>57</v>
@@ -15177,10 +15371,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>71</v>
@@ -15194,10 +15388,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>38</v>
@@ -15211,10 +15405,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>38</v>
@@ -15228,10 +15422,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>38</v>
@@ -15245,10 +15439,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>12</v>
@@ -15262,10 +15456,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>25</v>
@@ -15279,10 +15473,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>25</v>
@@ -15296,10 +15490,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>28</v>
@@ -15313,10 +15507,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>28</v>
@@ -15330,10 +15524,10 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>26</v>
@@ -15347,10 +15541,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>26</v>
@@ -15364,10 +15558,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>27</v>
@@ -15381,10 +15575,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>29</v>
@@ -15398,10 +15592,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B203" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C203" s="12" t="s">
         <v>29</v>
@@ -15415,10 +15609,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>29</v>
@@ -15432,10 +15626,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C205" s="12" t="s">
         <v>29</v>
@@ -15449,10 +15643,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>29</v>
@@ -15466,10 +15660,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>30</v>
@@ -15483,10 +15677,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C208" s="12" t="s">
         <v>30</v>
@@ -15500,10 +15694,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>71</v>
@@ -15517,10 +15711,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C210" s="12" t="s">
         <v>69</v>
@@ -15534,10 +15728,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C211" s="12" t="s">
         <v>69</v>
@@ -15551,10 +15745,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>69</v>
@@ -15568,10 +15762,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C213" s="12" t="s">
         <v>31</v>
@@ -15585,10 +15779,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C214" s="12" t="s">
         <v>31</v>
@@ -15602,10 +15796,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B215" s="12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>31</v>
@@ -15619,10 +15813,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>31</v>
@@ -15636,10 +15830,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>69</v>
@@ -15653,10 +15847,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>69</v>
@@ -15670,10 +15864,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="12" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>69</v>
@@ -15687,10 +15881,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>69</v>
@@ -15704,16 +15898,16 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="12" t="s">
-        <v>425</v>
+        <v>733</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>426</v>
+        <v>734</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D221" s="12" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="E221" s="12" t="s">
         <v>1</v>
@@ -15721,10 +15915,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="12" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>32</v>
@@ -15738,16 +15932,16 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="12" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B223" s="12" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E223" s="12" t="s">
         <v>1</v>
@@ -15755,16 +15949,16 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="12" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B224" s="12" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E224" s="12" t="s">
         <v>1</v>
@@ -15772,16 +15966,16 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="12" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B225" s="12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E225" s="12" t="s">
         <v>1</v>
@@ -15789,16 +15983,16 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="12" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B226" s="12" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="E226" s="12" t="s">
         <v>1</v>
@@ -15806,10 +16000,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="12" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B227" s="12" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C227" s="12" t="s">
         <v>60</v>
@@ -15823,10 +16017,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="12" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C228" s="12" t="s">
         <v>60</v>
@@ -15840,10 +16034,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="12" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B229" s="12" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C229" s="12" t="s">
         <v>60</v>
@@ -15857,16 +16051,16 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="12" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D230" s="12" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E230" s="12" t="s">
         <v>1</v>
@@ -15874,10 +16068,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="12" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B231" s="12" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C231" s="12" t="s">
         <v>71</v>
@@ -15891,16 +16085,16 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="12" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D232" s="12" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E232" s="12" t="s">
         <v>1</v>
@@ -15908,10 +16102,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="12" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B233" s="12" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C233" s="12" t="s">
         <v>60</v>
@@ -15925,10 +16119,10 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B234" s="12" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C234" s="12" t="s">
         <v>60</v>
@@ -15942,10 +16136,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="12" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B235" s="12" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C235" s="12" t="s">
         <v>60</v>
@@ -15959,16 +16153,16 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="12" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B236" s="12" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E236" s="12" t="s">
         <v>1</v>
@@ -15976,10 +16170,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="12" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B237" s="12" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C237" s="12" t="s">
         <v>35</v>
@@ -15993,10 +16187,10 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="12" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B238" s="12" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C238" s="12" t="s">
         <v>35</v>
@@ -16010,10 +16204,10 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="12" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B239" s="12" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C239" s="12" t="s">
         <v>35</v>
@@ -16027,16 +16221,16 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="12" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B240" s="12" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E240" s="12" t="s">
         <v>1</v>
@@ -16044,10 +16238,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="12" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B241" s="12" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C241" s="12" t="s">
         <v>55</v>
@@ -16061,10 +16255,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="12" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B242" s="12" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C242" s="12" t="s">
         <v>55</v>
@@ -16078,10 +16272,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="12" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C243" s="12" t="s">
         <v>55</v>
@@ -16095,10 +16289,10 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="12" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C244" s="12" t="s">
         <v>55</v>
@@ -16112,10 +16306,10 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="12" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B245" s="12" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C245" s="12" t="s">
         <v>55</v>
@@ -16129,10 +16323,10 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="12" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C246" s="12" t="s">
         <v>55</v>
@@ -16146,10 +16340,10 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="12" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B247" s="12" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C247" s="12" t="s">
         <v>55</v>
@@ -16163,16 +16357,16 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="12" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B248" s="12" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E248" s="12" t="s">
         <v>1</v>
@@ -16180,10 +16374,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="12" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C249" s="12" t="s">
         <v>46</v>
@@ -16197,16 +16391,16 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="12" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D250" s="12" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E250" s="12" t="s">
         <v>1</v>
@@ -16214,16 +16408,16 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="12" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B251" s="12" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D251" s="12" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E251" s="12" t="s">
         <v>1</v>
@@ -16231,16 +16425,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="12" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B252" s="12" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D252" s="12" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E252" s="12" t="s">
         <v>1</v>
@@ -16248,16 +16442,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="12" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B253" s="12" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D253" s="12" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E253" s="12" t="s">
         <v>1</v>
@@ -16265,13 +16459,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="12" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B254" s="12" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D254" s="12" t="s">
         <v>9</v>
@@ -16282,10 +16476,10 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="12" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B255" s="12" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C255" s="12" t="s">
         <v>36</v>
@@ -16299,10 +16493,10 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="12" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B256" s="12" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C256" s="12" t="s">
         <v>36</v>
@@ -16316,10 +16510,10 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="12" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B257" s="12" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>36</v>
@@ -16333,16 +16527,16 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="12" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D258" s="12" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E258" s="12" t="s">
         <v>1</v>
@@ -16350,10 +16544,10 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="12" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B259" s="12" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C259" s="12" t="s">
         <v>51</v>
@@ -16367,10 +16561,10 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B260" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C260" s="12" t="s">
         <v>51</v>
@@ -16384,10 +16578,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B261" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C261" s="12" t="s">
         <v>51</v>
@@ -16401,10 +16595,10 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B262" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C262" s="12" t="s">
         <v>51</v>
@@ -16418,16 +16612,16 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="12" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B263" s="12" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D263" s="12" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E263" s="12" t="s">
         <v>1</v>
@@ -16435,10 +16629,10 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="12" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C264" s="12" t="s">
         <v>37</v>
@@ -16452,10 +16646,10 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="12" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B265" s="12" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C265" s="12" t="s">
         <v>37</v>
@@ -16469,10 +16663,10 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" s="12" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C266" s="12" t="s">
         <v>37</v>
@@ -16486,10 +16680,10 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" s="12" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C267" s="12" t="s">
         <v>37</v>
@@ -16503,16 +16697,16 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="12" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="D268" s="12" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E268" s="12" t="s">
         <v>1</v>
@@ -16520,16 +16714,16 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="12" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D269" s="12" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E269" s="12" t="s">
         <v>1</v>
@@ -16537,16 +16731,16 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="12" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D270" s="12" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E270" s="12" t="s">
         <v>1</v>
@@ -16554,16 +16748,16 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="12" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B271" s="12" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D271" s="12" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E271" s="12" t="s">
         <v>1</v>
@@ -16571,16 +16765,16 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" s="12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D272" s="12" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="E272" s="12" t="s">
         <v>1</v>
@@ -16588,16 +16782,16 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" s="12" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D273" s="12" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="E273" s="12" t="s">
         <v>1</v>
@@ -16605,10 +16799,10 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="12" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B274" s="12" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C274" s="12" t="s">
         <v>71</v>
@@ -16622,10 +16816,10 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" s="12" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B275" s="12" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C275" s="12" t="s">
         <v>71</v>
@@ -16639,10 +16833,10 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" s="12" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B276" s="12" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C276" s="12" t="s">
         <v>71</v>
@@ -16656,10 +16850,10 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="12" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C277" s="12" t="s">
         <v>71</v>
@@ -16673,10 +16867,10 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="12" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B278" s="12" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C278" s="12" t="s">
         <v>71</v>
@@ -16690,16 +16884,16 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B279" s="12" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E279" s="12" t="s">
         <v>1</v>
@@ -16707,13 +16901,13 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="12" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D280" s="12" t="s">
         <v>9</v>
@@ -16724,10 +16918,10 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" s="12" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B281" s="12" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C281" s="12" t="s">
         <v>41</v>
@@ -16741,10 +16935,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" s="12" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C282" s="12" t="s">
         <v>41</v>
@@ -16758,16 +16952,16 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="12" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B283" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D283" s="12" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E283" s="12" t="s">
         <v>1</v>
@@ -16775,16 +16969,16 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B284" s="12" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D284" s="12" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E284" s="12" t="s">
         <v>1</v>
@@ -16792,10 +16986,10 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="12" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B285" s="12" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C285" s="12" t="s">
         <v>59</v>
@@ -16809,10 +17003,10 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="12" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B286" s="12" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C286" s="12" t="s">
         <v>59</v>
@@ -16826,10 +17020,10 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="12" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B287" s="12" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C287" s="12" t="s">
         <v>59</v>
@@ -16843,27 +17037,27 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="12" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B288" s="12" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D288" s="12" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E288" s="12" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="12" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B289" s="12" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C289" s="12" t="s">
         <v>73</v>
@@ -16877,13 +17071,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="12" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B290" s="12" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D290" s="12" t="s">
         <v>9</v>
@@ -16894,10 +17088,10 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="12" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B291" s="12" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C291" s="12" t="s">
         <v>74</v>
@@ -16911,13 +17105,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="12" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B292" s="12" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D292" s="12" t="s">
         <v>9</v>
@@ -16928,10 +17122,10 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" s="12" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B293" s="12" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C293" s="12" t="s">
         <v>75</v>
@@ -16945,10 +17139,10 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="12" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B294" s="12" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C294" s="12" t="s">
         <v>75</v>
@@ -16962,10 +17156,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B295" s="12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C295" s="12" t="s">
         <v>75</v>
@@ -16979,10 +17173,10 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="12" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B296" s="12" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C296" s="12" t="s">
         <v>75</v>
@@ -16996,13 +17190,13 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="12" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B297" s="12" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D297" s="12" t="s">
         <v>9</v>
@@ -17013,13 +17207,13 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="12" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B298" s="12" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D298" s="12" t="s">
         <v>9</v>
@@ -17030,10 +17224,10 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B299" s="12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C299" s="12" t="s">
         <v>76</v>
@@ -17047,13 +17241,13 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B300" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D300" s="12" t="s">
         <v>9</v>
@@ -17064,13 +17258,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B301" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D301" s="12" t="s">
         <v>9</v>
@@ -17081,10 +17275,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="12" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B302" s="12" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C302" s="12" t="s">
         <v>77</v>
@@ -17098,27 +17292,27 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B303" s="12" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D303" s="12" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="12" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B304" s="12" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C304" s="12" t="s">
         <v>82</v>
@@ -17132,10 +17326,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="12" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B305" s="12" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C305" s="12" t="s">
         <v>82</v>
@@ -17149,13 +17343,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="12" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B306" s="12" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D306" s="12" t="s">
         <v>79</v>
@@ -17166,10 +17360,10 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="12" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B307" s="12" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C307" s="12" t="s">
         <v>86</v>
@@ -17183,10 +17377,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="12" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B308" s="12" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C308" s="12" t="s">
         <v>86</v>
@@ -17200,13 +17394,13 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="12" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B309" s="12" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D309" s="12" t="s">
         <v>79</v>
@@ -17217,10 +17411,10 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="12" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B310" s="12" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C310" s="12" t="s">
         <v>84</v>
@@ -17234,13 +17428,13 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="12" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B311" s="12" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D311" s="12" t="s">
         <v>79</v>
@@ -17251,10 +17445,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="12" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B312" s="12" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C312" s="12" t="s">
         <v>81</v>
@@ -17268,10 +17462,10 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="12" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B313" s="12" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C313" s="12" t="s">
         <v>81</v>
@@ -17285,10 +17479,10 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="12" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B314" s="12" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C314" s="12" t="s">
         <v>81</v>
@@ -17302,10 +17496,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="12" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B315" s="12" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C315" s="12" t="s">
         <v>81</v>
@@ -17319,13 +17513,13 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="12" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B316" s="12" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C316" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D316" s="12" t="s">
         <v>79</v>
@@ -17336,10 +17530,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="12" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B317" s="12" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C317" s="12" t="s">
         <v>85</v>
@@ -17353,10 +17547,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="12" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B318" s="12" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C318" s="12" t="s">
         <v>85</v>
@@ -17370,10 +17564,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" s="12" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B319" s="12" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C319" s="12" t="s">
         <v>85</v>
@@ -17387,10 +17581,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="12" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B320" s="12" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C320" s="12" t="s">
         <v>85</v>
@@ -17404,13 +17598,13 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="12" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B321" s="12" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C321" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D321" s="12" t="s">
         <v>79</v>
@@ -17421,10 +17615,10 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="12" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B322" s="12" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C322" s="12" t="s">
         <v>87</v>
@@ -17438,10 +17632,10 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="12" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B323" s="12" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C323" s="12" t="s">
         <v>87</v>
@@ -17455,10 +17649,10 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="12" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B324" s="12" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C324" s="12" t="s">
         <v>87</v>
@@ -17472,10 +17666,10 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="12" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B325" s="12" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C325" s="12" t="s">
         <v>87</v>
@@ -17489,10 +17683,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="12" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B326" s="12" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C326" s="12" t="s">
         <v>87</v>
@@ -17506,10 +17700,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="12" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B327" s="12" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C327" s="12" t="s">
         <v>87</v>
@@ -17523,13 +17717,13 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="12" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B328" s="12" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C328" s="12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D328" s="12" t="s">
         <v>79</v>
@@ -17540,10 +17734,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="12" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B329" s="12" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C329" s="12" t="s">
         <v>80</v>
@@ -17557,10 +17751,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="12" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C330" s="12" t="s">
         <v>80</v>
@@ -17574,10 +17768,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="12" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B331" s="12" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C331" s="12" t="s">
         <v>80</v>
@@ -17591,13 +17785,13 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="12" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B332" s="12" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C332" s="12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D332" s="12" t="s">
         <v>79</v>
@@ -17608,13 +17802,13 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="12" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B333" s="12" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C333" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D333" s="12" t="s">
         <v>79</v>
@@ -17625,10 +17819,10 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="12" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B334" s="12" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C334" s="12" t="s">
         <v>83</v>
@@ -17642,10 +17836,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="12" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B335" s="12" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C335" s="12" t="s">
         <v>83</v>
@@ -17659,33 +17853,33 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="12" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B336" s="12" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C336" s="12" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D336" s="12" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E336" s="12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="12" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B337" s="12" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C337" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D337" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E337" s="12" t="s">
         <v>89</v>
@@ -17693,13 +17887,13 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="12" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B338" s="12" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C338" s="12" t="s">
-        <v>93</v>
+        <v>735</v>
       </c>
       <c r="D338" s="12" t="s">
         <v>92</v>
@@ -17710,16 +17904,16 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B339" s="12" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C339" s="12" t="s">
-        <v>96</v>
+        <v>735</v>
       </c>
       <c r="D339" s="12" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E339" s="12" t="s">
         <v>89</v>
@@ -17727,13 +17921,13 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="12" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B340" s="12" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C340" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D340" s="12" t="s">
         <v>70</v>
@@ -17744,13 +17938,13 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="12" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B341" s="12" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C341" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D341" s="12" t="s">
         <v>70</v>
@@ -17761,13 +17955,13 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="12" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B342" s="12" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C342" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D342" s="12" t="s">
         <v>70</v>
@@ -17778,13 +17972,13 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="12" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B343" s="12" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C343" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D343" s="12" t="s">
         <v>70</v>
@@ -17795,13 +17989,13 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="12" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B344" s="12" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C344" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D344" s="12" t="s">
         <v>70</v>
@@ -17812,13 +18006,13 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="12" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B345" s="12" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C345" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D345" s="12" t="s">
         <v>70</v>
@@ -17829,16 +18023,16 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="12" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B346" s="12" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C346" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E346" s="12" t="s">
         <v>89</v>
@@ -17846,13 +18040,13 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="12" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B347" s="12" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C347" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D347" s="12" t="s">
         <v>92</v>
@@ -17863,13 +18057,13 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="12" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B348" s="12" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D348" s="12" t="s">
         <v>92</v>
@@ -17880,13 +18074,13 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B349" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C349" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D349" s="12" t="s">
         <v>92</v>
@@ -17897,13 +18091,13 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="12" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B350" s="12" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C350" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D350" s="12" t="s">
         <v>92</v>
@@ -17914,13 +18108,13 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="12" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B351" s="12" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C351" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D351" s="12" t="s">
         <v>92</v>
@@ -17931,13 +18125,13 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="12" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B352" s="12" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C352" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D352" s="12" t="s">
         <v>92</v>
@@ -17948,13 +18142,13 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="12" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B353" s="12" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C353" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D353" s="12" t="s">
         <v>92</v>
@@ -17965,16 +18159,16 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="12" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B354" s="12" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C354" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E354" s="12" t="s">
         <v>89</v>
@@ -17982,16 +18176,16 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="12" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B355" s="12" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C355" s="12" t="s">
         <v>95</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E355" s="12" t="s">
         <v>89</v>
@@ -17999,13 +18193,13 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="12" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B356" s="12" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C356" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D356" s="12" t="s">
         <v>68</v>
@@ -18016,13 +18210,13 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="12" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B357" s="12" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C357" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D357" s="12" t="s">
         <v>68</v>
@@ -18033,699 +18227,716 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="12" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B358" s="12" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C358" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="E358" s="12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="12" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B359" s="12" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C359" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D359" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="12" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B360" s="12" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C360" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D360" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E360" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="12" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B361" s="12" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C361" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D361" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E361" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="12" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B362" s="12" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D362" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E362" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="12" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B363" s="12" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C363" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D363" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E363" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="12" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B364" s="12" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C364" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D364" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E364" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="12" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B365" s="12" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C365" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D365" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E365" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="12" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B366" s="12" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C366" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D366" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E366" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="12" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B367" s="12" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C367" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D367" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E367" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="12" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B368" s="12" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C368" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D368" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="12" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B369" s="12" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="12" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B370" s="12" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D370" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="12" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B371" s="12" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C371" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D371" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="12" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B372" s="12" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C372" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D372" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E372" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" s="12" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B373" s="12" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C373" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D373" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" s="12" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B374" s="12" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C374" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D374" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" s="12" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B375" s="12" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C375" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D375" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E375" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" s="12" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B376" s="12" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C376" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D376" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E376" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" s="12" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B377" s="12" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C377" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D377" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" s="12" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B378" s="12" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C378" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D378" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E378" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" s="12" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B379" s="12" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C379" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D379" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E379" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" s="12" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B380" s="12" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C380" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D380" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E380" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" s="12" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C381" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D381" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E381" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" s="12" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B382" s="12" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C382" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D382" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E382" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" s="12" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B383" s="12" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C383" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D383" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E383" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" s="12" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B384" s="12" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D384" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E384" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" s="12" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B385" s="12" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C385" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D385" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E385" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" s="12" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B386" s="12" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D386" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E386" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" s="12" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B387" s="12" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C387" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D387" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E387" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" s="12" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B388" s="12" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D388" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E388" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" s="12" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B389" s="12" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C389" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D389" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E389" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" s="12" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B390" s="12" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C390" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D390" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E390" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" s="12" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B391" s="12" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D391" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E391" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392" s="12" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B392" s="12" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D392" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E392" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393" s="12" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B393" s="12" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C393" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D393" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E393" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394" s="12" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B394" s="12" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E394" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395" s="12" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B395" s="12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C395" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D395" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E395" s="12" t="s">
-        <v>104</v>
+        <v>736</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396" s="12" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B396" s="12" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D396" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E396" s="12" t="s">
-        <v>104</v>
+        <v>736</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397" s="12" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B397" s="12" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C397" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D397" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E397" s="12" t="s">
-        <v>104</v>
+        <v>736</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398" s="12" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B398" s="12" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D398" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E398" s="12" t="s">
-        <v>104</v>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A399" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B399" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="C399" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D399" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E399" s="12" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -18734,4 +18945,776 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9499335-C316-4443-AB94-BF44BDD02086}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.6328125" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="70" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C2" s="21"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C3" s="24"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C4" s="21"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C5" s="21"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C8" s="21"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C9" s="21"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C11" s="25"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C12" s="25"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C13" s="25"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C15" s="25"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C16" s="25"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C17" s="25"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="C19" s="27"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>727</v>
+      </c>
+      <c r="C20" s="27"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="C21" s="27"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>727</v>
+      </c>
+      <c r="C22" s="27"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C23" s="28"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C24" s="28"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C25" s="28"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C26" s="28"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C27" s="28"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C28" s="28"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C29" s="28"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C30" s="28"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C31" s="28"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C32" s="28"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C33" s="28"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C34" s="28"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C35" s="28"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="C36" s="29"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>729</v>
+      </c>
+      <c r="C37" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BC2FA80-E5B6-4C1C-86B4-C7AD8A87A0F6}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.6328125" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="70" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="20" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="23" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="20" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="23" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="20" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="23" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="20" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="23" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="23"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="23"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="23"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="20" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="23" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>727</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="20" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="23" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>727</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="20" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="23"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="20"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="23"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="20"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="23"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="20"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="23"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="20"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="23"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="20"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="23"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="23"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="C36" s="29"/>
+      <c r="D36" s="20"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>729</v>
+      </c>
+      <c r="C37" s="29"/>
+      <c r="D37" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>